--- a/EPIC_0004_N_0006_Ride_Booking.xlsx
+++ b/EPIC_0004_N_0006_Ride_Booking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A62F63A-A019-4072-859D-2F8B0F055D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9060A3A9-7933-4F8D-8638-A933C5CD360E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -317,9 +317,6 @@
   </si>
   <si>
     <t>TC_RG_01_Ride_Booking</t>
-  </si>
-  <si>
-    <t>This test case validates the complete end-to-end booking and fulfillment flow for an Auto Ride service between the User and Driver mobile applications. It covers logging in both an approved driver and a customer with mock location set to Perambur, initiating an auto ride request to "Parsn Manere" from the User App, accepting the booking from the Driver App, extracting the ride verification OTP, updating status to "Arrived", and entering the OTP to start the trip. Finally, it verifies completing the trip, processing a cash payment settlement on both apps, and submitting mutual ratings and reviews to successfully close out the ride lifecycle.</t>
   </si>
   <si>
     <t>1.Reload User App Completely,reload_app,user,
@@ -810,6 +807,9 @@
 160. Wait for transaction action options to appear.
 161. Click "Settle Transaction" (Mark as Settle) button.
 162. Wait for financial settlement processing to complete.</t>
+  </si>
+  <si>
+    <t>This test case validates the end-to-end booking, fulfillment, and backend audit flow for an Auto Ride service across the User App, Driver App, and Super Admin Web Portal. It covers logging in both the driver and customer with forced locations in Perambur, initiating an "Auto Ride" to "Parsn Manere", and verifying real-time driver tracking via the Admin Aerial View across booking, pickup, and ongoing trip stages. It also validates dynamic OTP extraction, trip completion, cash payment settlement, mutual user-driver ratings, and back-office administrative tasks including review approval and transaction settlement in the earning reports.</t>
   </si>
 </sst>
 </file>
@@ -1314,13 +1314,13 @@
         <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
@@ -1329,7 +1329,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">

--- a/EPIC_0004_N_0006_Ride_Booking.xlsx
+++ b/EPIC_0004_N_0006_Ride_Booking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9060A3A9-7933-4F8D-8638-A933C5CD360E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0047BFBF-30E8-4A8B-8DBC-AE7BD9263963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,9 +314,6 @@
   </si>
   <si>
     <t>Driver Onboarding</t>
-  </si>
-  <si>
-    <t>TC_RG_01_Ride_Booking</t>
   </si>
   <si>
     <t>1.Reload User App Completely,reload_app,user,
@@ -810,6 +807,9 @@
   </si>
   <si>
     <t>This test case validates the end-to-end booking, fulfillment, and backend audit flow for an Auto Ride service across the User App, Driver App, and Super Admin Web Portal. It covers logging in both the driver and customer with forced locations in Perambur, initiating an "Auto Ride" to "Parsn Manere", and verifying real-time driver tracking via the Admin Aerial View across booking, pickup, and ongoing trip stages. It also validates dynamic OTP extraction, trip completion, cash payment settlement, mutual user-driver ratings, and back-office administrative tasks including review approval and transaction settlement in the earning reports.</t>
+  </si>
+  <si>
+    <t>TC_RG_02_Ride_Booking</t>
   </si>
 </sst>
 </file>
@@ -1311,16 +1311,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
@@ -1329,7 +1329,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
